--- a/modules/segment/docs/templates/Segment_Config_Template.xlsx
+++ b/modules/segment/docs/templates/Segment_Config_Template.xlsx
@@ -15,8 +15,30 @@
 </workbook>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Turas</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Valid Section keys: exec-summary, overview, validation, overlap, importance, golden-questions, profiles, vulnerability. Each key maps to a section in the HTML report. You may add multiple rows per section.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -24,25 +46,49 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Required?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
+    <t xml:space="preserve">Valid Values / Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA SOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">data_file</t>
   </si>
   <si>
     <t xml:space="preserve">data/survey_data.xlsx</t>
   </si>
   <si>
+    <t xml:space="preserve">REQUIRED</t>
+  </si>
+  <si>
     <t xml:space="preserve">Path to survey data file (.xlsx, .csv, or .sav)</t>
   </si>
   <si>
+    <t xml:space="preserve">.xlsx, .csv, .sav</t>
+  </si>
+  <si>
     <t xml:space="preserve">data_sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheet name in Excel file (default: Data)</t>
+    <t xml:space="preserve">Optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet name in Excel file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any valid sheet name</t>
   </si>
   <si>
     <t xml:space="preserve">id_variable</t>
@@ -54,28 +100,34 @@
     <t xml:space="preserve">Column name for respondent unique identifier</t>
   </si>
   <si>
+    <t xml:space="preserve">Column name in data</t>
+  </si>
+  <si>
     <t xml:space="preserve">clustering_vars</t>
   </si>
   <si>
     <t xml:space="preserve">q1,q2,q3,q4,q5</t>
   </si>
   <si>
-    <t xml:space="preserve">Comma-separated list of numeric variables for clustering</t>
+    <t xml:space="preserve">Comma-separated list of numeric variables for clustering. Aim for 8-20 variables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated column names</t>
   </si>
   <si>
     <t xml:space="preserve">profile_vars</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Comma-separated profile variables (optional, auto-detected if blank)</t>
+    <t xml:space="preserve">Comma-separated variables for profiling (auto-detected from data if blank)</t>
   </si>
   <si>
     <t xml:space="preserve">demographic_vars</t>
   </si>
   <si>
-    <t xml:space="preserve">Comma-separated demographic variables for profiling (optional)</t>
+    <t xml:space="preserve">Comma-separated categorical variables for demographic profiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUSTERING METHOD</t>
   </si>
   <si>
     <t xml:space="preserve">method</t>
@@ -84,7 +136,10 @@
     <t xml:space="preserve">kmeans</t>
   </si>
   <si>
-    <t xml:space="preserve">Clustering method: kmeans, hclust, gmm, or comma-separated for multi-method</t>
+    <t xml:space="preserve">Clustering algorithm. Use 'all' or comma-separated for multi-method comparison.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kmeans, hclust, gmm, all</t>
   </si>
   <si>
     <t xml:space="preserve">linkage_method</t>
@@ -93,19 +148,31 @@
     <t xml:space="preserve">ward.D2</t>
   </si>
   <si>
-    <t xml:space="preserve">Linkage method for hclust: ward.D2, complete, average, single</t>
+    <t xml:space="preserve">Linkage for hierarchical clustering. Only used when method=hclust.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ward.D2, complete, average, single, mcquitty, median, centroid</t>
   </si>
   <si>
     <t xml:space="preserve">gmm_model_type</t>
   </si>
   <si>
-    <t xml:space="preserve">GMM covariance model type (blank = auto-select best BIC)</t>
+    <t xml:space="preserve">GMM covariance structure. Only used when method=gmm. Blank = auto-select by BIC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EII, VII, EEI, VEI, EVI, VVI, EEE, VEE, EVE, VVE, EEV, VEV, EVV, VVV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K PARAMETERS</t>
   </si>
   <si>
     <t xml:space="preserve">k_fixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixed number of segments (leave blank for exploration mode)</t>
+    <t xml:space="preserve">Fixed number of segments. Leave blank for exploration mode (tests k_min to k_max).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer &gt;= 2</t>
   </si>
   <si>
     <t xml:space="preserve">k_min</t>
@@ -117,13 +184,31 @@
     <t xml:space="preserve">Minimum k to test in exploration mode</t>
   </si>
   <si>
+    <t xml:space="preserve">2-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">k_max</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum k to test in exploration mode</t>
+    <t xml:space="preserve">Maximum k to test in exploration mode. Must be &gt; k_min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k_selection_metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silhouette,elbow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metrics for choosing optimal k in exploration mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silhouette, elbow, calinski_harabasz, davies_bouldin, gap_statistic</t>
   </si>
   <si>
     <t xml:space="preserve">nstart</t>
@@ -135,13 +220,22 @@
     <t xml:space="preserve">Number of random starts for k-means (higher = more stable, slower)</t>
   </si>
   <si>
+    <t xml:space="preserve">1-200</t>
+  </si>
+  <si>
     <t xml:space="preserve">seed</t>
   </si>
   <si>
     <t xml:space="preserve">123</t>
   </si>
   <si>
-    <t xml:space="preserve">Random seed for reproducibility</t>
+    <t xml:space="preserve">Random seed for reproducibility. Set to any integer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any positive integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA HANDLING</t>
   </si>
   <si>
     <t xml:space="preserve">missing_data</t>
@@ -150,7 +244,10 @@
     <t xml:space="preserve">listwise_deletion</t>
   </si>
   <si>
-    <t xml:space="preserve">How to handle missing data: listwise_deletion, mean_imputation, median_imputation, refuse</t>
+    <t xml:space="preserve">Strategy for missing values in clustering variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listwise_deletion, mean_imputation, median_imputation, refuse</t>
   </si>
   <si>
     <t xml:space="preserve">missing_threshold</t>
@@ -159,7 +256,10 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum % missing data before warning (0-100)</t>
+    <t xml:space="preserve">Maximum % missing data per variable before warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-100</t>
   </si>
   <si>
     <t xml:space="preserve">standardize</t>
@@ -168,7 +268,10 @@
     <t xml:space="preserve">TRUE</t>
   </si>
   <si>
-    <t xml:space="preserve">Standardize variables before clustering? TRUE/FALSE</t>
+    <t xml:space="preserve">Standardize (z-score) variables before clustering? Recommended unless all on same scale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE, FALSE</t>
   </si>
   <si>
     <t xml:space="preserve">min_segment_size_pct</t>
@@ -177,7 +280,13 @@
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimum segment size as % of total (warns if below)</t>
+    <t xml:space="preserve">Minimum segment size as % of total. Warns if any segment is smaller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTLIER DETECTION</t>
   </si>
   <si>
     <t xml:space="preserve">outlier_detection</t>
@@ -186,7 +295,7 @@
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable outlier detection? TRUE/FALSE</t>
+    <t xml:space="preserve">Enable multivariate outlier detection before clustering?</t>
   </si>
   <si>
     <t xml:space="preserve">outlier_method</t>
@@ -195,7 +304,10 @@
     <t xml:space="preserve">zscore</t>
   </si>
   <si>
-    <t xml:space="preserve">Outlier detection method: zscore or mahalanobis</t>
+    <t xml:space="preserve">Detection method. Only used when outlier_detection=TRUE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zscore, mahalanobis</t>
   </si>
   <si>
     <t xml:space="preserve">outlier_threshold</t>
@@ -204,7 +316,10 @@
     <t xml:space="preserve">3.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Z-score threshold for outlier detection (typically 2.5-3.5)</t>
+    <t xml:space="preserve">Threshold for flagging outliers (z-score or chi-sq alpha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0-5.0</t>
   </si>
   <si>
     <t xml:space="preserve">outlier_handling</t>
@@ -213,7 +328,10 @@
     <t xml:space="preserve">flag</t>
   </si>
   <si>
-    <t xml:space="preserve">How to handle outliers: none, flag, or remove</t>
+    <t xml:space="preserve">How to handle detected outliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none, flag, remove</t>
   </si>
   <si>
     <t xml:space="preserve">outlier_min_vars</t>
@@ -222,13 +340,31 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">Minimum variables exceeding threshold to flag as outlier</t>
+    <t xml:space="preserve">Minimum variables exceeding threshold to flag a respondent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to number of clustering vars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outlier_alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical alpha for Mahalanobis outlier detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0001-0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARIABLE SELECTION</t>
   </si>
   <si>
     <t xml:space="preserve">variable_selection</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable automatic variable selection? TRUE/FALSE</t>
+    <t xml:space="preserve">Enable automatic variable selection to reduce redundancy?</t>
   </si>
   <si>
     <t xml:space="preserve">variable_selection_method</t>
@@ -237,13 +373,46 @@
     <t xml:space="preserve">variance_correlation</t>
   </si>
   <si>
-    <t xml:space="preserve">Selection method: variance_correlation, factor_analysis, or both</t>
+    <t xml:space="preserve">Selection algorithm. Only used when variable_selection=TRUE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variance_correlation, factor_analysis, both</t>
   </si>
   <si>
     <t xml:space="preserve">max_clustering_vars</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum number of clustering variables after selection</t>
+    <t xml:space="preserve">Maximum variables to retain after selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">varsel_min_variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum variance threshold — variables below this are dropped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01-1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">varsel_max_correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum pairwise correlation — one of a correlated pair is dropped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5-0.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTPUT</t>
   </si>
   <si>
     <t xml:space="preserve">output_folder</t>
@@ -252,7 +421,10 @@
     <t xml:space="preserve">output/</t>
   </si>
   <si>
-    <t xml:space="preserve">Output folder path (relative to config file)</t>
+    <t xml:space="preserve">Output folder path (relative to config file location)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any valid path</t>
   </si>
   <si>
     <t xml:space="preserve">output_prefix</t>
@@ -261,19 +433,34 @@
     <t xml:space="preserve">seg_</t>
   </si>
   <si>
-    <t xml:space="preserve">Prefix for output file names</t>
+    <t xml:space="preserve">Prefix for all output file names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
   </si>
   <si>
     <t xml:space="preserve">create_dated_folder</t>
   </si>
   <si>
-    <t xml:space="preserve">Create date-stamped subfolder? TRUE/FALSE</t>
+    <t xml:space="preserve">Create a date-stamped subfolder for each run?</t>
   </si>
   <si>
     <t xml:space="preserve">save_model</t>
   </si>
   <si>
-    <t xml:space="preserve">Save model object (.rds) for scoring? TRUE/FALSE</t>
+    <t xml:space="preserve">Save clustering model (.rds) for scoring new respondents?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generate_stats_pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate diagnostics stats pack. Contractual deliverable — provides audit trail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y, N</t>
   </si>
   <si>
     <t xml:space="preserve">segment_names</t>
@@ -282,7 +469,10 @@
     <t xml:space="preserve">auto</t>
   </si>
   <si>
-    <t xml:space="preserve">Segment names: 'auto' or comma-separated custom names</t>
+    <t xml:space="preserve">Segment labels: 'auto' generates names, or provide comma-separated custom names matching k.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'auto' or comma-separated names</t>
   </si>
   <si>
     <t xml:space="preserve">auto_name_style</t>
@@ -291,19 +481,28 @@
     <t xml:space="preserve">descriptive</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto-naming style: descriptive, persona, or simple</t>
+    <t xml:space="preserve">Style for auto-generated names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">descriptive, persona, simple</t>
   </si>
   <si>
     <t xml:space="preserve">scale_max</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum value on rating scale (for interpreting high/low scores)</t>
+    <t xml:space="preserve">Maximum value on rating scale (for interpreting high/low scores in naming)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTML REPORT</t>
   </si>
   <si>
     <t xml:space="preserve">html_report</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate interactive HTML report? TRUE/FALSE</t>
+    <t xml:space="preserve">Generate interactive HTML report with charts and profiles?</t>
   </si>
   <si>
     <t xml:space="preserve">brand_colour</t>
@@ -315,6 +514,9 @@
     <t xml:space="preserve">Brand colour for report header (hex code)</t>
   </si>
   <si>
+    <t xml:space="preserve">#000000 to #FFFFFF</t>
+  </si>
+  <si>
     <t xml:space="preserve">accent_colour</t>
   </si>
   <si>
@@ -330,31 +532,103 @@
     <t xml:space="preserve">Segmentation Report</t>
   </si>
   <si>
-    <t xml:space="preserve">Report title displayed in header</t>
+    <t xml:space="preserve">Title displayed in report header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_exec_summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show executive summary section in HTML report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show overview section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show validation metrics section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_importance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show variable importance section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show segment profiles section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_demographics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show demographic profiles section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show classification rules section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show action cards section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_stability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show stability analysis section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show membership probabilities section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">html_show_guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show interpretation guide section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENHANCED FEATURES</t>
   </si>
   <si>
     <t xml:space="preserve">generate_rules</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate classification rules (decision tree)? TRUE/FALSE</t>
+    <t xml:space="preserve">Generate classification rules (decision tree) for typing new respondents?</t>
   </si>
   <si>
     <t xml:space="preserve">rules_max_depth</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum depth for classification tree (1-5)</t>
+    <t xml:space="preserve">Maximum tree depth for classification rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-5</t>
   </si>
   <si>
     <t xml:space="preserve">generate_action_cards</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate executive action cards? TRUE/FALSE</t>
+    <t xml:space="preserve">Generate executive action cards per segment?</t>
   </si>
   <si>
     <t xml:space="preserve">run_stability_check</t>
   </si>
   <si>
-    <t xml:space="preserve">Run stability bootstrap check? TRUE/FALSE</t>
+    <t xml:space="preserve">Run bootstrap stability check? Computationally expensive.</t>
   </si>
   <si>
     <t xml:space="preserve">stability_n_runs</t>
@@ -363,13 +637,25 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of bootstrap runs for stability (3-20)</t>
+    <t xml:space="preserve">Number of bootstrap runs for stability analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-20</t>
   </si>
   <si>
     <t xml:space="preserve">golden_questions_n</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of golden questions to identify (1-10)</t>
+    <t xml:space="preserve">Number of golden questions to identify for typing tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use_lca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable latent class analysis (experimental). Requires poLCA package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METADATA</t>
   </si>
   <si>
     <t xml:space="preserve">project_name</t>
@@ -378,7 +664,7 @@
     <t xml:space="preserve">My Segmentation Project</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name for report headers</t>
+    <t xml:space="preserve">Project name for report headers and stats pack</t>
   </si>
   <si>
     <t xml:space="preserve">analyst_name</t>
@@ -393,19 +679,31 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">Project description (optional)</t>
+    <t xml:space="preserve">Project description (appears in report and stats pack)</t>
   </si>
   <si>
     <t xml:space="preserve">question_labels_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Path to Excel file with question labels (optional)</t>
+    <t xml:space="preserve">Path to Excel file with question labels (variable | label)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.xlsx file path</t>
   </si>
   <si>
     <t xml:space="preserve">segment_names_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Path to Excel file with edited segment names (optional, Step 3 workflow)</t>
+    <t xml:space="preserve">Path to Excel file with edited segment names (Step 3 workflow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research_house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name for stats pack Declaration sheet</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -414,52 +712,34 @@
     <t xml:space="preserve">label</t>
   </si>
   <si>
-    <t xml:space="preserve">satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Satisfaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loyalty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Loyalty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation Appeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price_sensitivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price Sensitivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recommend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likelihood to Recommend</t>
+    <t xml:space="preserve">q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall satisfaction with service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likelihood to recommend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value for money perception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality of customer support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ease of use rating</t>
   </si>
   <si>
     <t xml:space="preserve">Section</t>
@@ -471,67 +751,91 @@
     <t xml:space="preserve">exec-summary</t>
   </si>
   <si>
+    <t xml:space="preserve">Key findings and strategic recommendations go here.</t>
+  </si>
+  <si>
     <t xml:space="preserve">overview</t>
   </si>
   <si>
+    <t xml:space="preserve">High-level overview of the segmentation solution.</t>
+  </si>
+  <si>
     <t xml:space="preserve">validation</t>
   </si>
   <si>
+    <t xml:space="preserve">Commentary on segment stability and validity metrics.</t>
+  </si>
+  <si>
     <t xml:space="preserve">overlap</t>
   </si>
   <si>
+    <t xml:space="preserve">Notes on segment overlap and distinctiveness.</t>
+  </si>
+  <si>
     <t xml:space="preserve">importance</t>
   </si>
   <si>
+    <t xml:space="preserve">Which variables drive segment separation most.</t>
+  </si>
+  <si>
     <t xml:space="preserve">golden-questions</t>
   </si>
   <si>
+    <t xml:space="preserve">The best survey questions for classifying new respondents.</t>
+  </si>
+  <si>
     <t xml:space="preserve">profiles</t>
   </si>
   <si>
+    <t xml:space="preserve">Narrative descriptions of each segment profile.</t>
+  </si>
+  <si>
     <t xml:space="preserve">vulnerability</t>
   </si>
   <si>
+    <t xml:space="preserve">Observations on vulnerable or at-risk segments.</t>
+  </si>
+  <si>
     <t xml:space="preserve">analyst</t>
   </si>
   <si>
-    <t xml:space="preserve">Duncan Brett</t>
-  </si>
-  <si>
     <t xml:space="preserve">company</t>
   </si>
   <si>
-    <t xml:space="preserve">The Research Lamppost (Pty) Ltd</t>
+    <t xml:space="preserve">The Research LampPost</t>
   </si>
   <si>
     <t xml:space="preserve">email</t>
   </si>
   <si>
-    <t xml:space="preserve">duncan@researchlamppost.co.za</t>
+    <t xml:space="preserve">analyst@example.com</t>
   </si>
   <si>
     <t xml:space="preserve">project</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer Experience Segmentation Study</t>
+    <t xml:space="preserve">Customer Segmentation 2026</t>
   </si>
   <si>
     <t xml:space="preserve">client</t>
   </si>
   <si>
-    <t xml:space="preserve">Acme Corporation</t>
+    <t xml:space="preserve">Client Organisation</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">19 March 2026</t>
+    <t xml:space="preserve">2026-04-06</t>
   </si>
   <si>
     <t xml:space="preserve">confidentiality</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFIDENTIAL - For internal use only</t>
+    <t xml:space="preserve">Confidential — internal use only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
   </si>
   <si>
     <t xml:space="preserve">Title</t>
@@ -543,16 +847,19 @@
     <t xml:space="preserve">Image</t>
   </si>
   <si>
-    <t xml:space="preserve">Key Findings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter key findings here</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommendations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter recommendations here</t>
+    <t xml:space="preserve">Segmentation Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study identified N distinct customer segments based on attitudinal and behavioural variables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overview_chart.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategic Recommendations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritise Segment A for retention campaigns; Segment B shows strongest growth potential.</t>
   </si>
 </sst>
 </file>
@@ -560,7 +867,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -568,16 +875,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF323367"/>
+      <name val="Aptos"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Aptos"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF388E3C"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD32F2F"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF388E3C"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF323367"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EAF6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -585,12 +946,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF323367"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -881,553 +1265,1522 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="89.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="60.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="35.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
+      <c r="A9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
+      <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
+      <c r="A19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
+      <c r="A20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
+      <c r="A21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
+      <c r="A23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
+        <v>79</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
+      <c r="A25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
+      <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
+        <v>91</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
+      <c r="A29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
+        <v>99</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" t="s">
-        <v>91</v>
+      <c r="C33" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
+        <v>110</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
+      <c r="A35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
+        <v>117</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
+      <c r="A37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
+      <c r="A38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
-        <v>105</v>
-      </c>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" t="s">
-        <v>106</v>
+      <c r="A39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
+        <v>130</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" t="s">
-        <v>110</v>
+      <c r="A41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
+        <v>75</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
+      <c r="A43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" t="s">
-        <v>117</v>
+        <v>142</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" t="s">
-        <v>120</v>
+      <c r="A45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
-      </c>
-      <c r="C46" t="s">
-        <v>123</v>
+        <v>79</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="s">
-        <v>125</v>
+      <c r="A47" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
+        <v>75</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="s">
-        <v>129</v>
+      <c r="A49" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
+        <v>174</v>
+      </c>
+      <c r="E56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>177</v>
+      </c>
+      <c r="B58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s">
+        <v>189</v>
+      </c>
+      <c r="E64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
+        <v>204</v>
+      </c>
+      <c r="E70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
+        <v>208</v>
+      </c>
+      <c r="E72" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" t="s">
+        <v>213</v>
+      </c>
+      <c r="E74" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>221</v>
+      </c>
+      <c r="E78" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="29">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"kmeans,hclust,gmm,all"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B10:B10</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"listwise_deletion,mean_imputation,median_imputation,refuse"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B21:B21</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"zscore,mahalanobis"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B27:B27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"none,flag,remove"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B29:B29</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"ward.D2,complete,average,single,mcquitty,median,centroid"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B11:B11</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"variance_correlation,factor_analysis,both"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B34:B34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"descriptive,persona,simple"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B45:B45</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B43:B43</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B23:B23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B26:B26</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B33:B33</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B41:B41</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B42:B42</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B48:B48</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B64:B64</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B66:B66</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B67:B67</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B70:B70</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B52:B52</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B53:B53</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B54:B54</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B55:B55</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B56:B56</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B57:B57</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B58:B58</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B59:B59</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B60:B60</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B61:B61</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B62:B62</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1436,81 +2789,56 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.15" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="50.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" t="s">
-        <v>131</v>
+      <c r="A1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" t="s">
-        <v>135</v>
+      <c r="A3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" t="s">
-        <v>139</v>
+      <c r="A5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1524,86 +2852,86 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.15" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="65.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" t="s">
-        <v>149</v>
+      <c r="A1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="A3" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
+      <c r="A5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
+      <c r="A7" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+      <c r="A9" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
 </worksheet>
 </file>
 
@@ -1612,73 +2940,80 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="38.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.15" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="50.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" t="s">
-        <v>161</v>
+      <c r="A3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B5" t="s">
-        <v>165</v>
+      <c r="A5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" t="s">
-        <v>169</v>
+      <c r="A7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1692,42 +3027,42 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="26.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="5.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="65.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C1" t="s">
-        <v>174</v>
+      <c r="A1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="A3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
